--- a/data/trans_orig/IQ09_M-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,22 +716,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,0</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 4,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,37 +741,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,08</t>
+          <t>0,17; 1,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,12</t>
+          <t>0,18; 1,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,83</t>
+          <t>0,11; 0,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,75</t>
+          <t>0,44; 2,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,29</t>
+          <t>0,22; 2,22</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,6</t>
+          <t>0,41; 2,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,5</t>
+          <t>0,04; 1,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,74</t>
+          <t>0,25; 2,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,63</t>
+          <t>0,69; 5,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,14</t>
+          <t>0,51; 4,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,41</t>
+          <t>0,34; 1,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,92</t>
+          <t>0,21; 1,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,26</t>
+          <t>0,85; 3,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,29</t>
+          <t>0,28; 2,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,1</t>
+          <t>0,23; 1,12</t>
         </is>
       </c>
     </row>
@@ -996,22 +996,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,8</t>
+          <t>0,0; 4,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,07</t>
+          <t>0,41; 3,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 8,02</t>
+          <t>0,33; 7,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,33</t>
+          <t>0,53; 2,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,37 +1021,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,35</t>
+          <t>1,25; 3,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 4,5</t>
+          <t>0,13; 4,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,43</t>
+          <t>0,22; 5,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,8</t>
+          <t>0,9; 5,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,83</t>
+          <t>1,1; 2,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,97</t>
+          <t>0,9; 5,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,24</t>
+          <t>0,73; 4,32</t>
         </is>
       </c>
     </row>
@@ -1141,17 +1141,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,2</t>
+          <t>0,73; 4,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,47</t>
+          <t>0,44; 4,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,18</t>
+          <t>0,09; 1,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,37 +1161,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,95</t>
+          <t>0,59; 3,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,97</t>
+          <t>0,87; 4,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,54</t>
+          <t>0,76; 4,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,93</t>
+          <t>0,13; 2,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,33</t>
+          <t>0,89; 3,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,77</t>
+          <t>1,02; 3,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,17</t>
+          <t>0,7; 3,28</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,0</t>
+          <t>0,28; 2,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,0</t>
+          <t>0,7; 2,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,79</t>
+          <t>0,75; 2,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,36</t>
+          <t>0,28; 1,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,37</t>
+          <t>0,51; 2,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,66</t>
+          <t>1,17; 2,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,95</t>
+          <t>0,96; 2,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,42</t>
+          <t>0,72; 2,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,89</t>
+          <t>0,58; 1,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,09</t>
+          <t>1,08; 2,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,39</t>
+          <t>1,08; 2,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,67</t>
+          <t>0,65; 1,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Habitat-trans_orig.xlsx
@@ -726,12 +726,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,87</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,37 +741,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,1</t>
+          <t>0,17; 1,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,72</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,06</t>
+          <t>0,2; 1,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,78</t>
+          <t>0,11; 0,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,85</t>
+          <t>0,48; 2,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,22</t>
+          <t>0,23; 2,25</t>
         </is>
       </c>
     </row>
@@ -861,57 +861,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,72</t>
+          <t>0,3; 2,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,52</t>
+          <t>0,07; 1,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,76</t>
+          <t>0,25; 2,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,07</t>
+          <t>0,67; 5,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,18</t>
+          <t>0,49; 4,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,4</t>
+          <t>0,31; 1,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,98</t>
+          <t>0,27; 2,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,33</t>
+          <t>0,81; 3,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,29</t>
+          <t>0,29; 2,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,12</t>
+          <t>0,23; 1,11</t>
         </is>
       </c>
     </row>
@@ -996,22 +996,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,62</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,11</t>
+          <t>0,47; 3,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 7,99</t>
+          <t>0,68; 8,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,35</t>
+          <t>0,53; 2,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,37 +1021,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,55</t>
+          <t>1,22; 3,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,31</t>
+          <t>0,26; 4,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 5,98</t>
+          <t>0,26; 6,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,4</t>
+          <t>0,9; 5,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,81</t>
+          <t>1,08; 2,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,05</t>
+          <t>0,88; 4,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,32</t>
+          <t>0,64; 4,37</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1141,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,17</t>
+          <t>0,75; 4,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,53</t>
+          <t>0,5; 4,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,14</t>
+          <t>0,09; 1,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,45</t>
+          <t>0,59; 3,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,27</t>
+          <t>0,88; 4,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,37</t>
+          <t>0,83; 4,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,96</t>
+          <t>0,14; 3,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,09</t>
+          <t>0,97; 3,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,71</t>
+          <t>1,06; 3,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,28</t>
+          <t>0,64; 3,22</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,16</t>
+          <t>0,23; 1,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,05</t>
+          <t>0,76; 2,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,86</t>
+          <t>0,74; 2,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,37</t>
+          <t>0,28; 1,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,28</t>
+          <t>0,5; 2,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,63</t>
+          <t>1,15; 2,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,73</t>
+          <t>1,06; 2,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,34</t>
+          <t>0,81; 2,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,97</t>
+          <t>0,59; 1,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,07</t>
+          <t>1,1; 2,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,43</t>
+          <t>1,09; 2,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,7</t>
+          <t>0,67; 1,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Habitat-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,63</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,73</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,75</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,17; 1,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,24; 1,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,14</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,15</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,74</t>
+          <t>0,11; 0,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,83</t>
+          <t>0,45; 2,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,25</t>
+          <t>0,24; 2,36</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,35</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,86</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,18</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,35</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,86</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,25; 2,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,65</t>
+          <t>0,83; 5,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,48</t>
+          <t>0,51; 4,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,53</t>
+          <t>0,28; 1,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,82</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,33</t>
+          <t>0,31; 2,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,19</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,4</t>
+          <t>0,38; 2,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,02</t>
+          <t>0,27; 1,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,17</t>
+          <t>0,79; 3,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,18</t>
+          <t>0,3; 2,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,11</t>
+          <t>0,43; 1,29</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,19</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,81</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,48</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,78</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>1,65</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>0,75; 7,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,1</t>
+          <t>1,2; 3,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 8,09</t>
+          <t>0,14; 4,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,23</t>
+          <t>0,12; 5,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,51</t>
+          <t>0,39; 4,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,47</t>
+          <t>0,47; 3,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,42</t>
+          <t>0,66; 8,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 6,01</t>
+          <t>0,41; 2,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,01</t>
+          <t>0,89; 4,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,79</t>
+          <t>1,14; 2,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,96</t>
+          <t>1,09; 4,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,37</t>
+          <t>0,6; 4,29</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,97</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,52</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,16</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,45</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,32</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,36</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,19</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,97</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,85</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,67; 3,95</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,71; 3,97</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,88; 4,5</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 4,14</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,5; 4,56</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 1,11</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,82</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,98</t>
+          <t>0,73; 4,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,08</t>
+          <t>0,52; 4,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,41</t>
+          <t>0,12; 1,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,0</t>
+          <t>0,13; 2,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,12</t>
+          <t>0,96; 3,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,66</t>
+          <t>1,1; 3,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,22</t>
+          <t>0,74; 3,07</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,74</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,84</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,52</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -1276,42 +1276,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,94</t>
+          <t>0,51; 2,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,04</t>
+          <t>1,15; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,8</t>
+          <t>1,11; 2,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,31</t>
+          <t>0,76; 2,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,28</t>
+          <t>0,28; 2,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,72</t>
+          <t>0,74; 2,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,87</t>
+          <t>0,73; 2,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,41</t>
+          <t>0,54; 1,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,25</t>
+          <t>1,1; 2,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,39</t>
+          <t>1,1; 2,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,69</t>
+          <t>0,8; 1,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
+          <t>Tiempo medio en meses que los menores llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,267 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5603184179866124</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.108792072803616</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.6349777960429144</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.269733642779481</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.1309025298573822</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1.734625312305085</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0.8549703127162228</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0.5851792159695275</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0.3675596538356182</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>1.375331599580093</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0.748090862008941</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,17; 1,08</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,86</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,24; 1,21</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,55</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,25</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,64</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,61</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0,11; 0,83</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0,45; 2,75</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,24; 2,36</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0.1667682294082952</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.2425104419233962</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0.1082319232431299</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.4538170965411271</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0.2356279645542948</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>1.077387745370673</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.858757145843027</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.212331487118279</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.553864491866635</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>4.251631957769058</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3.635559955247174</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>2.605669715454018</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0.8266931437806716</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>2.747153175732795</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>2.360742191685881</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,35</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,86</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,25; 2,74</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,83; 5,63</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,51; 4,14</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,28; 1,34</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,31</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,31; 2,6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,43</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 2,09</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,27; 1,92</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0,79; 3,26</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>0,3; 2,29</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,43; 1,29</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.16629047212136</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.346312282440976</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.86130908251915</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.7043961798707401</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.3014836727098873</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.184555909943076</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0.1518577541778549</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.038517025429914</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.8660220990560633</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>1.752317842484316</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0.9319626765533704</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0.8226307483247249</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,78</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2,59</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.2494924564362348</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8266967553348861</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.5068861071038542</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.2831644912177266</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.3106960837028517</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.3830151590184943</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.2713908896093763</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0.7893850081988195</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0.2976116897510963</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0.4326760238323084</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 7,51</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,2; 3,35</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,14; 4,5</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,12; 5,56</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,39; 4,8</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,47; 3,07</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,66; 8,02</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,41; 2,23</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0,89; 4,8</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1,14; 2,83</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,09; 4,97</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,6; 4,29</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.743056086499044</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.633811967171694</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.139568487031753</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.341479627276178</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1.310634861814816</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>2.603708275816144</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.4268825894910626</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>2.09423620505012</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>1.922738144691748</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>3.255314200928172</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>2.288299946267453</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>1.285401349685738</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +919,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,97</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,45</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.195329707960971</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.190444358928188</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.801564777692452</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.806701360894523</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1.608463568186</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.476851186397613</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>3.77835775354594</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1.40967374133369</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>2.336538159033105</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1.883503977356946</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>2.592896093612983</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1.647907813001469</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,85</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,67; 3,95</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,71; 3,97</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,88; 4,5</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,73; 4,2</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,52; 4,47</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,12; 1,1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0,13; 2,93</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0,96; 3,33</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 3,77</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,74; 3,07</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.7539594175438895</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.204856102536062</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1365078391193403</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.1161762549658236</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.3941166514681093</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.4686735630359729</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0.6624909246312924</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.401507093464228</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.8910854174546278</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1.140295817116323</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1.085667993221192</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0.6034567320837737</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.509103631102279</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.34766564924099</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.499399236432843</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.525031512401711</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>3.074027567986393</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>8.024345587894668</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2.200134547463977</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>4.803423587047059</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>2.825455366495683</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>4.968101697229556</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>4.290610124704221</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.96716822414704</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.520433324185346</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.161411895991486</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.447694177963422</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.3197589600495402</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>2.361470044930763</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>2.186001932325732</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0.5386960342421664</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.8038917806065724</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1.838552271325306</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>2.17174216044782</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>1.650997714509427</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.6696273269279162</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.7065306232329553</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.8766877561753578</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.7343460083382463</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0.5172581885098075</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0.1163074191096418</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0.1314390109690685</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0.9616903764151996</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1.095911978920633</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0.7407305144586068</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.854299720297647</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.951110753592702</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.97077771971229</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.502291938282562</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>4.199339816641492</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>4.466103632944041</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>1.102331253015879</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>2.932865029194885</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>3.326123499642019</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>3.767100917472018</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>3.071655784409085</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,51; 2,37</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 2,66</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,11; 2,95</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,76; 2,43</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,28; 2,0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,74; 2,0</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,73; 2,79</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,54; 1,61</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0,59; 1,89</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 2,09</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 2,39</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,8; 1,79</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.167296433376911</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.740065232741119</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.797711188963817</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.353373606541376</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.8409027343496931</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.266231700892254</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>1.52049336977896</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0.9538646105745465</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1.045449007429395</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>1.528415837243488</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>1.670083644795906</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1.190212298740964</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.5129839542099085</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.153774129576893</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.107789005976223</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.7629031590558345</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.2775037270853154</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.7441950134945083</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.7288295946140068</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.5423756588500399</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.587063887217144</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>1.097662253162223</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>1.09607276225612</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0.7969359973545388</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.367807184986848</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.664175506895318</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.947229504222053</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.430300423455491</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.003335847039142</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.000566663112875</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>2.787070895355545</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>1.607979472326294</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1.890215384103898</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>2.086061910788167</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>2.389178314634862</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>1.794806100107733</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1325,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
